--- a/artfynd/S 3229-2024 artfynd.xlsx
+++ b/artfynd/S 3229-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY148"/>
+  <dimension ref="A1:AZ148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63184231</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63200729</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,6 +1060,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123504</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1155,6 +1175,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580532</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580591</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580516</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1483,6 +1518,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828514</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1618,6 +1658,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828512</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1725,6 +1770,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199884</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1851,6 +1901,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539639</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1953,6 +2008,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199830</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2064,6 +2124,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199916</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2171,6 +2236,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199843</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2292,6 +2362,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63181476</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2418,6 +2493,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538384</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2543,6 +2623,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828509</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2654,6 +2739,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199810</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2780,6 +2870,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63184248</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2912,6 +3007,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828505</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3038,6 +3138,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63200827</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3164,6 +3269,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539869</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3285,6 +3395,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828567</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3406,6 +3521,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828568</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3527,6 +3647,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828569</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3648,6 +3773,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123501</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3764,6 +3894,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123503</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3875,6 +4010,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580610</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4000,6 +4140,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828506</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4102,6 +4247,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199796</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4209,6 +4359,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199926</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4335,6 +4490,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98537467</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4461,6 +4621,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63202100</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4587,6 +4752,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63202963</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4713,6 +4883,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539583</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4839,6 +5014,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539584</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4965,6 +5145,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539587</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5091,6 +5276,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539588</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5217,6 +5407,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539589</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5343,6 +5538,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539591</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5469,6 +5669,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539594</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5595,6 +5800,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539595</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5721,6 +5931,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539597</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5847,6 +6062,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539598</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5973,6 +6193,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539599</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6099,6 +6324,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539600</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6225,6 +6455,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539601</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6351,6 +6586,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539638</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6477,6 +6717,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539653</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6603,6 +6848,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539685</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6729,6 +6979,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189576</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6855,6 +7110,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189604</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6981,6 +7241,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538321</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7107,6 +7372,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538322</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7233,6 +7503,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538323</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7359,6 +7634,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538324</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7485,6 +7765,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538325</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7611,6 +7896,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538326</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7737,6 +8027,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538327</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7863,6 +8158,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538328</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7989,6 +8289,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538329</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8115,6 +8420,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538330</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8241,6 +8551,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538335</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8367,6 +8682,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63225982</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8493,6 +8813,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63228867</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8599,6 +8924,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580702</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8705,6 +9035,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580568</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8811,6 +9146,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580570</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8917,6 +9257,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580573</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9028,6 +9373,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580656</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9129,6 +9479,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580534</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9230,6 +9585,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580536</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9336,6 +9696,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580556</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9447,6 +9812,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580577</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9558,6 +9928,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580578</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9684,6 +10059,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538381</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9809,6 +10189,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828501</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9911,6 +10296,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116438691</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10042,6 +10432,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98537516</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10168,6 +10563,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539866</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10289,6 +10689,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828564</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10410,6 +10815,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828565</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10531,6 +10941,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828566</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10652,6 +11067,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828570</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10773,6 +11193,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828571</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10894,6 +11319,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828572</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11015,6 +11445,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828573</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11136,6 +11571,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828574</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11257,6 +11697,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828575</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11378,6 +11823,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828578</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11499,6 +11949,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828579</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11620,6 +12075,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828580</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11741,6 +12201,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828581</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11862,6 +12327,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828582</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11983,6 +12453,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828583</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12104,6 +12579,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828584</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12225,6 +12705,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123500</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12346,6 +12831,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123516</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12452,6 +12942,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580583</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12558,6 +13053,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580529</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12683,6 +13183,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828502</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12794,6 +13299,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580606</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12900,6 +13410,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580557</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13026,6 +13541,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539657</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13152,6 +13672,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539681</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13278,6 +13803,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538334</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13404,6 +13934,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538336</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13530,6 +14065,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538337</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13661,6 +14201,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538347</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13792,6 +14337,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538763</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13918,6 +14468,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538821</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14029,6 +14584,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116441780</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -14143,6 +14703,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116471136</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14244,6 +14809,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580549</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14345,6 +14915,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580552</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14455,6 +15030,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580546</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14557,6 +15137,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116436783</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14658,6 +15243,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116470894</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14759,6 +15349,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580624</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14871,6 +15466,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199806</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14992,6 +15592,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828547</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -15113,6 +15718,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828548</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15234,6 +15844,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828550</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15355,6 +15970,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828551</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15476,6 +16096,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828553</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15597,6 +16222,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828554</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15718,6 +16348,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828555</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15839,6 +16474,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828556</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15960,6 +16600,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828557</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -16081,6 +16726,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828558</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -16202,6 +16852,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828559</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16323,6 +16978,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828560</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16444,6 +17104,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828561</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16565,6 +17230,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828562</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16677,6 +17347,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199876</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16808,6 +17483,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828490</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16933,6 +17613,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828495</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -17058,6 +17743,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828497</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -17159,6 +17849,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580696</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -17260,6 +17955,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580697</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17361,6 +18061,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580681</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -17462,6 +18167,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580670</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -17577,6 +18287,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580736</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17688,6 +18403,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580662</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17794,6 +18514,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580615</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17905,6 +18630,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580714</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -18016,6 +18746,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580715</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -18127,8 +18862,162 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580605</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>